--- a/study/03_adam/spec/adam_spec.xlsx
+++ b/study/03_adam/spec/adam_spec.xlsx
@@ -1481,7 +1481,7 @@
     <t xml:space="preserve">Adverse event dictionary</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1 (synthetic coding)</t>
+    <t xml:space="preserve">28.1 (synthetic coding)</t>
   </si>
   <si>
     <t xml:space="preserve">Type</t>

--- a/study/03_adam/spec/adam_spec.xlsx
+++ b/study/03_adam/spec/adam_spec.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="594">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="601">
   <si>
     <t xml:space="preserve">Attribute</t>
   </si>
@@ -1064,6 +1064,15 @@
     <t xml:space="preserve">MT.PKEXRSN</t>
   </si>
   <si>
+    <t xml:space="preserve">NCAEXRSN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reason Value Excluded by NCA Rule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MT.NCAEXRSN</t>
+  </si>
+  <si>
     <t xml:space="preserve">MT.ADT.PP</t>
   </si>
   <si>
@@ -1454,6 +1463,12 @@
     <t xml:space="preserve">AUC BELOW 5% OF GEOMETRIC MEAN AUC</t>
   </si>
   <si>
+    <t xml:space="preserve">ADJUSTED R-SQUARED BELOW 0.90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUC(0-INF) EXTRAPOLATED ABOVE 20%</t>
+  </si>
+  <si>
     <t xml:space="preserve">MILD</t>
   </si>
   <si>
@@ -1730,19 +1745,25 @@
     <t xml:space="preserve">Algorithm for ANL01FL.PP</t>
   </si>
   <si>
-    <t xml:space="preserve">Y when Cmax and AUC(0-t) exist for the period and PKEXRSN is missing: descriptive PK summaries.</t>
+    <t xml:space="preserve">Y when Cmax and AUC(0-t) exist for the period, PKEXRSN is missing, and NCAEXRSN is missing for the record: descriptive PK summaries.</t>
   </si>
   <si>
     <t xml:space="preserve">Algorithm for ANL02FL.PP</t>
   </si>
   <si>
-    <t xml:space="preserve">Y when ANL01FL = Y and the participant has ANL01FL = Y periods for both products: bioequivalence analysis.</t>
+    <t xml:space="preserve">Y when ANL01FL = Y and the participant has evaluable periods (Cmax and AUC(0-t), PKEXRSN missing) for both products: bioequivalence analysis. The supportive AUC(0-inf) analysis uses participants with ANL02FL = Y for AUCIFO in both periods.</t>
   </si>
   <si>
     <t xml:space="preserve">Algorithm for PKEXRSN</t>
   </si>
   <si>
-    <t xml:space="preserve">SAP exclusion rules in order: emesis within 2 h of dosing (ADAE); pre-dose concentration above 5% of the period's Cmax; AUC(0-t) below 5% of the product's geometric mean AUC without the participant (ICH M13A).</t>
+    <t xml:space="preserve">SAP period rules in order: emesis within 2 h of dosing (ADAE; a protocol violation documented before bioanalysis, ICH M13A 2.2.1); pre-dose concentration above 5% of the period's Cmax (ICH M13A 2.2.3.3) and AUC(0-t) below 5% of the product's geometric mean AUC without the participant (ICH M13A 2.2.1.1), both applied to the bioanalytical results.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Algorithm for NCAEXRSN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PP.PPEXCL (PKNCA exclude() in 04_analysis/01_nca.R) decoded: adjusted R-squared of the terminal fit below the SAP minimum flags lambda z and every parameter that depends on it; AUC(0-inf) more than the SAP maximum extrapolated flags AUC(0-inf). The value stays in AVAL.</t>
   </si>
   <si>
     <t xml:space="preserve">Algorithm for ADT.PP</t>
@@ -2184,24 +2205,24 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="B1" t="s">
-        <v>589</v>
+        <v>596</v>
       </c>
       <c r="C1" t="s">
-        <v>590</v>
+        <v>597</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>591</v>
+        <v>598</v>
       </c>
       <c r="B2" t="s">
-        <v>592</v>
+        <v>599</v>
       </c>
       <c r="C2" t="s">
-        <v>593</v>
+        <v>600</v>
       </c>
     </row>
   </sheetData>
@@ -7263,31 +7284,31 @@
         <v>31</v>
       </c>
       <c r="C133" t="s">
-        <v>259</v>
+        <v>347</v>
       </c>
       <c r="D133" t="s">
-        <v>260</v>
+        <v>348</v>
       </c>
       <c r="E133" t="s">
-        <v>88</v>
+        <v>55</v>
       </c>
       <c r="F133" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="G133"/>
-      <c r="H133" t="s">
-        <v>145</v>
-      </c>
+      <c r="H133"/>
       <c r="I133" t="s">
-        <v>30</v>
-      </c>
-      <c r="J133"/>
+        <v>24</v>
+      </c>
+      <c r="J133" t="s">
+        <v>347</v>
+      </c>
       <c r="K133" t="s">
         <v>123</v>
       </c>
       <c r="L133"/>
       <c r="M133" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="N133"/>
       <c r="O133"/>
@@ -7301,10 +7322,10 @@
         <v>31</v>
       </c>
       <c r="C134" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="E134" t="s">
         <v>88</v>
@@ -7313,7 +7334,9 @@
         <v>8</v>
       </c>
       <c r="G134"/>
-      <c r="H134"/>
+      <c r="H134" t="s">
+        <v>145</v>
+      </c>
       <c r="I134" t="s">
         <v>30</v>
       </c>
@@ -7323,7 +7346,7 @@
       </c>
       <c r="L134"/>
       <c r="M134" t="s">
-        <v>266</v>
+        <v>350</v>
       </c>
       <c r="N134"/>
       <c r="O134"/>
@@ -7337,16 +7360,16 @@
         <v>31</v>
       </c>
       <c r="C135" t="s">
-        <v>307</v>
+        <v>264</v>
       </c>
       <c r="D135" t="s">
-        <v>308</v>
+        <v>265</v>
       </c>
       <c r="E135" t="s">
-        <v>55</v>
+        <v>88</v>
       </c>
       <c r="F135" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G135"/>
       <c r="H135"/>
@@ -7359,7 +7382,7 @@
       </c>
       <c r="L135"/>
       <c r="M135" t="s">
-        <v>348</v>
+        <v>266</v>
       </c>
       <c r="N135"/>
       <c r="O135"/>
@@ -7373,16 +7396,16 @@
         <v>31</v>
       </c>
       <c r="C136" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="D136" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="E136" t="s">
-        <v>88</v>
+        <v>55</v>
       </c>
       <c r="F136" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G136"/>
       <c r="H136"/>
@@ -7395,7 +7418,7 @@
       </c>
       <c r="L136"/>
       <c r="M136" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="N136"/>
       <c r="O136"/>
@@ -7409,16 +7432,16 @@
         <v>31</v>
       </c>
       <c r="C137" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="D137" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="E137" t="s">
-        <v>55</v>
+        <v>88</v>
       </c>
       <c r="F137" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G137"/>
       <c r="H137"/>
@@ -7427,10 +7450,12 @@
       </c>
       <c r="J137"/>
       <c r="K137" t="s">
-        <v>304</v>
+        <v>123</v>
       </c>
       <c r="L137"/>
-      <c r="M137"/>
+      <c r="M137" t="s">
+        <v>351</v>
+      </c>
       <c r="N137"/>
       <c r="O137"/>
       <c r="P137"/>
@@ -7443,16 +7468,16 @@
         <v>31</v>
       </c>
       <c r="C138" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D138" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="E138" t="s">
         <v>55</v>
       </c>
       <c r="F138" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G138"/>
       <c r="H138"/>
@@ -7477,16 +7502,16 @@
         <v>31</v>
       </c>
       <c r="C139" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D139" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E139" t="s">
-        <v>88</v>
+        <v>55</v>
       </c>
       <c r="F139" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G139"/>
       <c r="H139"/>
@@ -7495,13 +7520,11 @@
       </c>
       <c r="J139"/>
       <c r="K139" t="s">
-        <v>51</v>
+        <v>304</v>
       </c>
       <c r="L139"/>
       <c r="M139"/>
-      <c r="N139" t="s">
-        <v>349</v>
-      </c>
+      <c r="N139"/>
       <c r="O139"/>
       <c r="P139"/>
     </row>
@@ -7513,10 +7536,10 @@
         <v>31</v>
       </c>
       <c r="C140" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="D140" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="E140" t="s">
         <v>88</v>
@@ -7531,34 +7554,34 @@
       </c>
       <c r="J140"/>
       <c r="K140" t="s">
-        <v>123</v>
+        <v>51</v>
       </c>
       <c r="L140"/>
-      <c r="M140" t="s">
-        <v>327</v>
-      </c>
-      <c r="N140"/>
+      <c r="M140"/>
+      <c r="N140" t="s">
+        <v>352</v>
+      </c>
       <c r="O140"/>
       <c r="P140"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="B141" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C141" t="s">
-        <v>53</v>
+        <v>325</v>
       </c>
       <c r="D141" t="s">
-        <v>54</v>
+        <v>326</v>
       </c>
       <c r="E141" t="s">
-        <v>55</v>
+        <v>88</v>
       </c>
       <c r="F141" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G141"/>
       <c r="H141"/>
@@ -7567,34 +7590,34 @@
       </c>
       <c r="J141"/>
       <c r="K141" t="s">
-        <v>51</v>
+        <v>123</v>
       </c>
       <c r="L141"/>
-      <c r="M141"/>
-      <c r="N141" t="s">
-        <v>56</v>
-      </c>
+      <c r="M141" t="s">
+        <v>327</v>
+      </c>
+      <c r="N141"/>
       <c r="O141"/>
       <c r="P141"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B142" t="s">
         <v>35</v>
       </c>
       <c r="C142" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D142" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E142" t="s">
         <v>55</v>
       </c>
       <c r="F142" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="G142"/>
       <c r="H142"/>
@@ -7608,67 +7631,65 @@
       <c r="L142"/>
       <c r="M142"/>
       <c r="N142" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="O142"/>
       <c r="P142"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B143" t="s">
         <v>35</v>
       </c>
       <c r="C143" t="s">
-        <v>121</v>
+        <v>57</v>
       </c>
       <c r="D143" t="s">
-        <v>122</v>
+        <v>58</v>
       </c>
       <c r="E143" t="s">
         <v>55</v>
       </c>
       <c r="F143" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="G143"/>
       <c r="H143"/>
       <c r="I143" t="s">
         <v>30</v>
       </c>
-      <c r="J143" t="s">
-        <v>104</v>
-      </c>
+      <c r="J143"/>
       <c r="K143" t="s">
         <v>51</v>
       </c>
       <c r="L143"/>
       <c r="M143"/>
       <c r="N143" t="s">
-        <v>210</v>
+        <v>59</v>
       </c>
       <c r="O143"/>
       <c r="P143"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B144" t="s">
         <v>35</v>
       </c>
       <c r="C144" t="s">
-        <v>198</v>
+        <v>121</v>
       </c>
       <c r="D144" t="s">
-        <v>199</v>
+        <v>122</v>
       </c>
       <c r="E144" t="s">
         <v>55</v>
       </c>
       <c r="F144" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G144"/>
       <c r="H144"/>
@@ -7676,7 +7697,7 @@
         <v>30</v>
       </c>
       <c r="J144" t="s">
-        <v>196</v>
+        <v>104</v>
       </c>
       <c r="K144" t="s">
         <v>51</v>
@@ -7684,62 +7705,64 @@
       <c r="L144"/>
       <c r="M144"/>
       <c r="N144" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O144"/>
       <c r="P144"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B145" t="s">
         <v>35</v>
       </c>
       <c r="C145" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="D145" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="E145" t="s">
-        <v>88</v>
+        <v>55</v>
       </c>
       <c r="F145" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G145"/>
       <c r="H145"/>
       <c r="I145" t="s">
         <v>30</v>
       </c>
-      <c r="J145"/>
+      <c r="J145" t="s">
+        <v>196</v>
+      </c>
       <c r="K145" t="s">
-        <v>123</v>
+        <v>51</v>
       </c>
       <c r="L145"/>
-      <c r="M145" t="s">
-        <v>350</v>
-      </c>
-      <c r="N145"/>
+      <c r="M145"/>
+      <c r="N145" t="s">
+        <v>211</v>
+      </c>
       <c r="O145"/>
       <c r="P145"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B146" t="s">
         <v>35</v>
       </c>
       <c r="C146" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D146" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E146" t="s">
-        <v>55</v>
+        <v>88</v>
       </c>
       <c r="F146" t="n">
         <v>8</v>
@@ -7749,15 +7772,13 @@
       <c r="I146" t="s">
         <v>30</v>
       </c>
-      <c r="J146" t="s">
-        <v>215</v>
-      </c>
+      <c r="J146"/>
       <c r="K146" t="s">
         <v>123</v>
       </c>
       <c r="L146"/>
       <c r="M146" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="N146"/>
       <c r="O146"/>
@@ -7765,22 +7786,22 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B147" t="s">
         <v>35</v>
       </c>
       <c r="C147" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D147" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E147" t="s">
         <v>55</v>
       </c>
       <c r="F147" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G147"/>
       <c r="H147"/>
@@ -7788,14 +7809,14 @@
         <v>30</v>
       </c>
       <c r="J147" t="s">
-        <v>127</v>
+        <v>215</v>
       </c>
       <c r="K147" t="s">
         <v>123</v>
       </c>
       <c r="L147"/>
       <c r="M147" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="N147"/>
       <c r="O147"/>
@@ -7803,22 +7824,22 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B148" t="s">
         <v>35</v>
       </c>
       <c r="C148" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="D148" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E148" t="s">
-        <v>88</v>
+        <v>55</v>
       </c>
       <c r="F148" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G148"/>
       <c r="H148"/>
@@ -7826,14 +7847,14 @@
         <v>30</v>
       </c>
       <c r="J148" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="K148" t="s">
         <v>123</v>
       </c>
       <c r="L148"/>
       <c r="M148" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="N148"/>
       <c r="O148"/>
@@ -7841,16 +7862,16 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B149" t="s">
         <v>35</v>
       </c>
       <c r="C149" t="s">
-        <v>325</v>
+        <v>220</v>
       </c>
       <c r="D149" t="s">
-        <v>326</v>
+        <v>221</v>
       </c>
       <c r="E149" t="s">
         <v>88</v>
@@ -7863,13 +7884,15 @@
       <c r="I149" t="s">
         <v>30</v>
       </c>
-      <c r="J149"/>
+      <c r="J149" t="s">
+        <v>133</v>
+      </c>
       <c r="K149" t="s">
         <v>123</v>
       </c>
       <c r="L149"/>
       <c r="M149" t="s">
-        <v>327</v>
+        <v>353</v>
       </c>
       <c r="N149"/>
       <c r="O149"/>
@@ -7877,16 +7900,16 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B150" t="s">
         <v>35</v>
       </c>
       <c r="C150" t="s">
-        <v>351</v>
+        <v>325</v>
       </c>
       <c r="D150" t="s">
-        <v>352</v>
+        <v>326</v>
       </c>
       <c r="E150" t="s">
         <v>88</v>
@@ -7901,19 +7924,19 @@
       </c>
       <c r="J150"/>
       <c r="K150" t="s">
-        <v>51</v>
+        <v>123</v>
       </c>
       <c r="L150"/>
-      <c r="M150"/>
-      <c r="N150" t="s">
-        <v>353</v>
-      </c>
+      <c r="M150" t="s">
+        <v>327</v>
+      </c>
+      <c r="N150"/>
       <c r="O150"/>
       <c r="P150"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B151" t="s">
         <v>35</v>
@@ -7925,10 +7948,10 @@
         <v>355</v>
       </c>
       <c r="E151" t="s">
-        <v>55</v>
+        <v>88</v>
       </c>
       <c r="F151" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="G151"/>
       <c r="H151"/>
@@ -7949,7 +7972,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B152" t="s">
         <v>35</v>
@@ -7985,7 +8008,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B153" t="s">
         <v>35</v>
@@ -8000,7 +8023,7 @@
         <v>55</v>
       </c>
       <c r="F153" t="n">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="G153"/>
       <c r="H153"/>
@@ -8021,7 +8044,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B154" t="s">
         <v>35</v>
@@ -8057,7 +8080,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B155" t="s">
         <v>35</v>
@@ -8072,39 +8095,37 @@
         <v>55</v>
       </c>
       <c r="F155" t="n">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="G155"/>
       <c r="H155"/>
       <c r="I155" t="s">
         <v>30</v>
       </c>
-      <c r="J155" t="s">
-        <v>368</v>
-      </c>
+      <c r="J155"/>
       <c r="K155" t="s">
         <v>51</v>
       </c>
       <c r="L155"/>
       <c r="M155"/>
       <c r="N155" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="O155"/>
       <c r="P155"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B156" t="s">
         <v>35</v>
       </c>
       <c r="C156" t="s">
+        <v>369</v>
+      </c>
+      <c r="D156" t="s">
         <v>370</v>
-      </c>
-      <c r="D156" t="s">
-        <v>371</v>
       </c>
       <c r="E156" t="s">
         <v>55</v>
@@ -8118,7 +8139,7 @@
         <v>30</v>
       </c>
       <c r="J156" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="K156" t="s">
         <v>51</v>
@@ -8126,26 +8147,26 @@
       <c r="L156"/>
       <c r="M156"/>
       <c r="N156" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="O156"/>
       <c r="P156"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B157" t="s">
         <v>35</v>
       </c>
       <c r="C157" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D157" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E157" t="s">
-        <v>88</v>
+        <v>55</v>
       </c>
       <c r="F157" t="n">
         <v>8</v>
@@ -8155,21 +8176,23 @@
       <c r="I157" t="s">
         <v>30</v>
       </c>
-      <c r="J157"/>
+      <c r="J157" t="s">
+        <v>371</v>
+      </c>
       <c r="K157" t="s">
-        <v>123</v>
+        <v>51</v>
       </c>
       <c r="L157"/>
-      <c r="M157" t="s">
-        <v>374</v>
-      </c>
-      <c r="N157"/>
+      <c r="M157"/>
+      <c r="N157" t="s">
+        <v>372</v>
+      </c>
       <c r="O157"/>
       <c r="P157"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B158" t="s">
         <v>35</v>
@@ -8181,33 +8204,31 @@
         <v>376</v>
       </c>
       <c r="E158" t="s">
-        <v>55</v>
+        <v>88</v>
       </c>
       <c r="F158" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G158"/>
       <c r="H158"/>
       <c r="I158" t="s">
         <v>30</v>
       </c>
-      <c r="J158" t="s">
-        <v>196</v>
-      </c>
+      <c r="J158"/>
       <c r="K158" t="s">
-        <v>51</v>
+        <v>123</v>
       </c>
       <c r="L158"/>
-      <c r="M158"/>
-      <c r="N158" t="s">
+      <c r="M158" t="s">
         <v>377</v>
       </c>
+      <c r="N158"/>
       <c r="O158"/>
       <c r="P158"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B159" t="s">
         <v>35</v>
@@ -8222,7 +8243,7 @@
         <v>55</v>
       </c>
       <c r="F159" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G159"/>
       <c r="H159"/>
@@ -8230,7 +8251,7 @@
         <v>30</v>
       </c>
       <c r="J159" t="s">
-        <v>380</v>
+        <v>196</v>
       </c>
       <c r="K159" t="s">
         <v>51</v>
@@ -8238,23 +8259,23 @@
       <c r="L159"/>
       <c r="M159"/>
       <c r="N159" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="O159"/>
       <c r="P159"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B160" t="s">
         <v>35</v>
       </c>
       <c r="C160" t="s">
+        <v>381</v>
+      </c>
+      <c r="D160" t="s">
         <v>382</v>
-      </c>
-      <c r="D160" t="s">
-        <v>383</v>
       </c>
       <c r="E160" t="s">
         <v>55</v>
@@ -8268,7 +8289,7 @@
         <v>30</v>
       </c>
       <c r="J160" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="K160" t="s">
         <v>51</v>
@@ -8276,50 +8297,52 @@
       <c r="L160"/>
       <c r="M160"/>
       <c r="N160" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="O160"/>
       <c r="P160"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B161" t="s">
         <v>35</v>
       </c>
       <c r="C161" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D161" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E161" t="s">
         <v>55</v>
       </c>
       <c r="F161" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G161"/>
       <c r="H161"/>
       <c r="I161" t="s">
         <v>30</v>
       </c>
-      <c r="J161"/>
+      <c r="J161" t="s">
+        <v>383</v>
+      </c>
       <c r="K161" t="s">
         <v>51</v>
       </c>
       <c r="L161"/>
       <c r="M161"/>
       <c r="N161" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="O161"/>
       <c r="P161"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B162" t="s">
         <v>35</v>
@@ -8334,7 +8357,7 @@
         <v>55</v>
       </c>
       <c r="F162" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G162"/>
       <c r="H162"/>
@@ -8355,7 +8378,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B163" t="s">
         <v>35</v>
@@ -8367,10 +8390,10 @@
         <v>391</v>
       </c>
       <c r="E163" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F163" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G163"/>
       <c r="H163"/>
@@ -8391,7 +8414,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B164" t="s">
         <v>35</v>
@@ -8427,7 +8450,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B165" t="s">
         <v>35</v>
@@ -8439,33 +8462,31 @@
         <v>397</v>
       </c>
       <c r="E165" t="s">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="F165" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G165"/>
-      <c r="H165" t="s">
-        <v>138</v>
-      </c>
+      <c r="H165"/>
       <c r="I165" t="s">
         <v>30</v>
       </c>
       <c r="J165"/>
       <c r="K165" t="s">
-        <v>123</v>
+        <v>51</v>
       </c>
       <c r="L165"/>
-      <c r="M165" t="s">
+      <c r="M165"/>
+      <c r="N165" t="s">
         <v>398</v>
       </c>
-      <c r="N165"/>
       <c r="O165"/>
       <c r="P165"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B166" t="s">
         <v>35</v>
@@ -8484,7 +8505,7 @@
       </c>
       <c r="G166"/>
       <c r="H166" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="I166" t="s">
         <v>30</v>
@@ -8495,7 +8516,7 @@
       </c>
       <c r="L166"/>
       <c r="M166" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="N166"/>
       <c r="O166"/>
@@ -8503,16 +8524,16 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B167" t="s">
         <v>35</v>
       </c>
       <c r="C167" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D167" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E167" t="s">
         <v>88</v>
@@ -8521,7 +8542,9 @@
         <v>8</v>
       </c>
       <c r="G167"/>
-      <c r="H167"/>
+      <c r="H167" t="s">
+        <v>145</v>
+      </c>
       <c r="I167" t="s">
         <v>30</v>
       </c>
@@ -8531,7 +8554,7 @@
       </c>
       <c r="L167"/>
       <c r="M167" t="s">
-        <v>266</v>
+        <v>401</v>
       </c>
       <c r="N167"/>
       <c r="O167"/>
@@ -8539,16 +8562,16 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B168" t="s">
         <v>35</v>
       </c>
       <c r="C168" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D168" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E168" t="s">
         <v>88</v>
@@ -8557,9 +8580,7 @@
         <v>8</v>
       </c>
       <c r="G168"/>
-      <c r="H168" t="s">
-        <v>138</v>
-      </c>
+      <c r="H168"/>
       <c r="I168" t="s">
         <v>30</v>
       </c>
@@ -8569,7 +8590,7 @@
       </c>
       <c r="L168"/>
       <c r="M168" t="s">
-        <v>405</v>
+        <v>266</v>
       </c>
       <c r="N168"/>
       <c r="O168"/>
@@ -8577,7 +8598,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B169" t="s">
         <v>35</v>
@@ -8596,7 +8617,7 @@
       </c>
       <c r="G169"/>
       <c r="H169" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="I169" t="s">
         <v>30</v>
@@ -8607,7 +8628,7 @@
       </c>
       <c r="L169"/>
       <c r="M169" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="N169"/>
       <c r="O169"/>
@@ -8615,16 +8636,16 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B170" t="s">
         <v>35</v>
       </c>
       <c r="C170" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D170" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E170" t="s">
         <v>88</v>
@@ -8633,7 +8654,9 @@
         <v>8</v>
       </c>
       <c r="G170"/>
-      <c r="H170"/>
+      <c r="H170" t="s">
+        <v>145</v>
+      </c>
       <c r="I170" t="s">
         <v>30</v>
       </c>
@@ -8643,7 +8666,7 @@
       </c>
       <c r="L170"/>
       <c r="M170" t="s">
-        <v>266</v>
+        <v>408</v>
       </c>
       <c r="N170"/>
       <c r="O170"/>
@@ -8651,41 +8674,77 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B171" t="s">
         <v>35</v>
       </c>
       <c r="C171" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D171" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E171" t="s">
-        <v>55</v>
+        <v>88</v>
       </c>
       <c r="F171" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G171"/>
       <c r="H171"/>
       <c r="I171" t="s">
-        <v>24</v>
-      </c>
-      <c r="J171" t="s">
-        <v>243</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="J171"/>
       <c r="K171" t="s">
         <v>123</v>
       </c>
       <c r="L171"/>
       <c r="M171" t="s">
-        <v>412</v>
+        <v>266</v>
       </c>
       <c r="N171"/>
       <c r="O171"/>
       <c r="P171"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>31</v>
+      </c>
+      <c r="B172" t="s">
+        <v>35</v>
+      </c>
+      <c r="C172" t="s">
+        <v>413</v>
+      </c>
+      <c r="D172" t="s">
+        <v>414</v>
+      </c>
+      <c r="E172" t="s">
+        <v>55</v>
+      </c>
+      <c r="F172" t="n">
+        <v>1</v>
+      </c>
+      <c r="G172"/>
+      <c r="H172"/>
+      <c r="I172" t="s">
+        <v>24</v>
+      </c>
+      <c r="J172" t="s">
+        <v>243</v>
+      </c>
+      <c r="K172" t="s">
+        <v>123</v>
+      </c>
+      <c r="L172"/>
+      <c r="M172" t="s">
+        <v>415</v>
+      </c>
+      <c r="N172"/>
+      <c r="O172"/>
+      <c r="P172"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8709,7 +8768,7 @@
         <v>40</v>
       </c>
       <c r="D1" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="E1" t="s">
         <v>10</v>
@@ -8761,7 +8820,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="B1" t="s">
         <v>9</v>
@@ -8770,7 +8829,7 @@
         <v>40</v>
       </c>
       <c r="D1" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E1" t="s">
         <v>1</v>
@@ -8789,13 +8848,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="B1" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C1" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="D1" t="s">
         <v>42</v>
@@ -8804,13 +8863,13 @@
         <v>39</v>
       </c>
       <c r="F1" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="G1" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="H1" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="2">
@@ -8850,7 +8909,7 @@
         <v>2</v>
       </c>
       <c r="F3" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="G3"/>
       <c r="H3" t="s">
@@ -8894,11 +8953,11 @@
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="G5"/>
       <c r="H5" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="6">
@@ -8916,11 +8975,11 @@
         <v>2</v>
       </c>
       <c r="F6" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="G6"/>
       <c r="H6" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="7">
@@ -8938,11 +8997,11 @@
         <v>1</v>
       </c>
       <c r="F7" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="G7"/>
       <c r="H7" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="8">
@@ -8960,11 +9019,11 @@
         <v>2</v>
       </c>
       <c r="F8" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="G8"/>
       <c r="H8" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="9">
@@ -8982,11 +9041,11 @@
         <v>3</v>
       </c>
       <c r="F9" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="G9"/>
       <c r="H9" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="10">
@@ -9004,11 +9063,11 @@
         <v>4</v>
       </c>
       <c r="F10" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="G10"/>
       <c r="H10" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="11">
@@ -9026,11 +9085,11 @@
         <v>1</v>
       </c>
       <c r="F11" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="G11"/>
       <c r="H11" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="12">
@@ -9048,11 +9107,11 @@
         <v>2</v>
       </c>
       <c r="F12" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="G12"/>
       <c r="H12" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="13">
@@ -9070,11 +9129,11 @@
         <v>3</v>
       </c>
       <c r="F13" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="G13"/>
       <c r="H13" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="14">
@@ -9092,11 +9151,11 @@
         <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="G14"/>
       <c r="H14" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="15">
@@ -9114,11 +9173,11 @@
         <v>1</v>
       </c>
       <c r="F15" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="G15"/>
       <c r="H15" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="16">
@@ -9136,11 +9195,11 @@
         <v>1</v>
       </c>
       <c r="F16" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="G16"/>
       <c r="H16" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="17">
@@ -9158,11 +9217,11 @@
         <v>2</v>
       </c>
       <c r="F17" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G17"/>
       <c r="H17" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="18">
@@ -9180,11 +9239,11 @@
         <v>1</v>
       </c>
       <c r="F18" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="G18"/>
       <c r="H18" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="19">
@@ -9202,11 +9261,11 @@
         <v>2</v>
       </c>
       <c r="F19" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G19"/>
       <c r="H19" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="20">
@@ -9224,11 +9283,11 @@
         <v>3</v>
       </c>
       <c r="F20" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="G20"/>
       <c r="H20" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="21">
@@ -9246,11 +9305,11 @@
         <v>4</v>
       </c>
       <c r="F21" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="G21"/>
       <c r="H21" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="22">
@@ -9268,11 +9327,11 @@
         <v>1</v>
       </c>
       <c r="F22" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="G22"/>
       <c r="H22" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="23">
@@ -9290,11 +9349,11 @@
         <v>2</v>
       </c>
       <c r="F23" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="G23"/>
       <c r="H23" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="24">
@@ -9312,11 +9371,11 @@
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="G24"/>
       <c r="H24" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="25">
@@ -9334,11 +9393,11 @@
         <v>2</v>
       </c>
       <c r="F25" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="G25"/>
       <c r="H25" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="26">
@@ -9356,11 +9415,11 @@
         <v>1</v>
       </c>
       <c r="F26" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="G26"/>
       <c r="H26" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="27">
@@ -9378,11 +9437,11 @@
         <v>2</v>
       </c>
       <c r="F27" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="G27"/>
       <c r="H27" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="28">
@@ -9400,11 +9459,11 @@
         <v>3</v>
       </c>
       <c r="F28" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="G28"/>
       <c r="H28" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="29">
@@ -9422,11 +9481,11 @@
         <v>1</v>
       </c>
       <c r="F29" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="G29"/>
       <c r="H29" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="30">
@@ -9444,11 +9503,11 @@
         <v>2</v>
       </c>
       <c r="F30" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="G30"/>
       <c r="H30" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="31">
@@ -9466,11 +9525,11 @@
         <v>1</v>
       </c>
       <c r="F31" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="G31"/>
       <c r="H31" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="32">
@@ -9488,11 +9547,11 @@
         <v>1</v>
       </c>
       <c r="F32" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="G32"/>
       <c r="H32" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="33">
@@ -9510,11 +9569,11 @@
         <v>2</v>
       </c>
       <c r="F33" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="G33"/>
       <c r="H33" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="34">
@@ -9554,11 +9613,11 @@
         <v>1</v>
       </c>
       <c r="F35" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="G35"/>
       <c r="H35" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="36">
@@ -9576,11 +9635,11 @@
         <v>2</v>
       </c>
       <c r="F36" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="G36"/>
       <c r="H36" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="37">
@@ -9598,11 +9657,11 @@
         <v>1</v>
       </c>
       <c r="F37" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="G37"/>
       <c r="H37" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="38">
@@ -9620,11 +9679,11 @@
         <v>2</v>
       </c>
       <c r="F38" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="G38"/>
       <c r="H38" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="39">
@@ -9642,11 +9701,11 @@
         <v>3</v>
       </c>
       <c r="F39" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="G39"/>
       <c r="H39" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="40">
@@ -9664,11 +9723,11 @@
         <v>4</v>
       </c>
       <c r="F40" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="G40"/>
       <c r="H40" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="41">
@@ -9686,11 +9745,11 @@
         <v>5</v>
       </c>
       <c r="F41" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="G41"/>
       <c r="H41" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="42">
@@ -9708,11 +9767,11 @@
         <v>6</v>
       </c>
       <c r="F42" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="G42"/>
       <c r="H42" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="43">
@@ -9730,11 +9789,11 @@
         <v>7</v>
       </c>
       <c r="F43" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="G43"/>
       <c r="H43" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="44">
@@ -9752,11 +9811,11 @@
         <v>8</v>
       </c>
       <c r="F44" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="G44"/>
       <c r="H44" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="45">
@@ -9774,11 +9833,11 @@
         <v>9</v>
       </c>
       <c r="F45" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="G45"/>
       <c r="H45" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="46">
@@ -9796,11 +9855,11 @@
         <v>10</v>
       </c>
       <c r="F46" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="G46"/>
       <c r="H46" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="47">
@@ -9818,11 +9877,11 @@
         <v>11</v>
       </c>
       <c r="F47" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="G47"/>
       <c r="H47" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="48">
@@ -9840,11 +9899,11 @@
         <v>12</v>
       </c>
       <c r="F48" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="G48"/>
       <c r="H48" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="49">
@@ -9862,11 +9921,11 @@
         <v>13</v>
       </c>
       <c r="F49" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="G49"/>
       <c r="H49" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="50">
@@ -9884,11 +9943,11 @@
         <v>1</v>
       </c>
       <c r="F50" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="G50"/>
       <c r="H50" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="51">
@@ -9906,11 +9965,11 @@
         <v>2</v>
       </c>
       <c r="F51" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="G51"/>
       <c r="H51" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="52">
@@ -9928,19 +9987,19 @@
         <v>3</v>
       </c>
       <c r="F52" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="G52"/>
       <c r="H52" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>368</v>
+        <v>347</v>
       </c>
       <c r="B53" t="s">
-        <v>368</v>
+        <v>347</v>
       </c>
       <c r="C53"/>
       <c r="D53" t="s">
@@ -9950,19 +10009,19 @@
         <v>1</v>
       </c>
       <c r="F53" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="G53"/>
       <c r="H53" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>368</v>
+        <v>347</v>
       </c>
       <c r="B54" t="s">
-        <v>368</v>
+        <v>347</v>
       </c>
       <c r="C54"/>
       <c r="D54" t="s">
@@ -9972,77 +10031,121 @@
         <v>2</v>
       </c>
       <c r="F54" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="G54"/>
       <c r="H54" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B55" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C55"/>
       <c r="D55" t="s">
         <v>55</v>
       </c>
       <c r="E55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F55" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="G55"/>
       <c r="H55" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="B56" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="C56"/>
       <c r="D56" t="s">
         <v>55</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="G56"/>
       <c r="H56" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="B57" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="C57"/>
       <c r="D57" t="s">
         <v>55</v>
       </c>
       <c r="E57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F57" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="G57"/>
       <c r="H57" t="s">
-        <v>481</v>
+        <v>484</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>383</v>
+      </c>
+      <c r="B58" t="s">
+        <v>383</v>
+      </c>
+      <c r="C58"/>
+      <c r="D58" t="s">
+        <v>55</v>
+      </c>
+      <c r="E58" t="n">
+        <v>1</v>
+      </c>
+      <c r="F58" t="s">
+        <v>485</v>
+      </c>
+      <c r="G58"/>
+      <c r="H58" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>383</v>
+      </c>
+      <c r="B59" t="s">
+        <v>383</v>
+      </c>
+      <c r="C59"/>
+      <c r="D59" t="s">
+        <v>55</v>
+      </c>
+      <c r="E59" t="n">
+        <v>2</v>
+      </c>
+      <c r="F59" t="s">
+        <v>486</v>
+      </c>
+      <c r="G59"/>
+      <c r="H59" t="s">
+        <v>486</v>
       </c>
     </row>
   </sheetData>
@@ -10058,36 +10161,36 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="B1" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C1" t="s">
         <v>42</v>
       </c>
       <c r="D1" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="E1" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="B2" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="C2" t="s">
         <v>55</v>
       </c>
       <c r="D2" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="E2" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
     </row>
   </sheetData>
@@ -10103,25 +10206,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="B1" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C1" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="D1" t="s">
         <v>10</v>
       </c>
       <c r="E1" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="F1" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="G1" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="H1" t="s">
         <v>49</v>
@@ -10132,13 +10235,13 @@
         <v>124</v>
       </c>
       <c r="B2" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="C2" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="D2" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="E2"/>
       <c r="F2"/>
@@ -10150,13 +10253,13 @@
         <v>128</v>
       </c>
       <c r="B3" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="C3" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="D3" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="E3"/>
       <c r="F3"/>
@@ -10168,13 +10271,13 @@
         <v>139</v>
       </c>
       <c r="B4" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="C4" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="D4" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="E4"/>
       <c r="F4"/>
@@ -10186,13 +10289,13 @@
         <v>142</v>
       </c>
       <c r="B5" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="C5" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="D5" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="E5"/>
       <c r="F5"/>
@@ -10204,13 +10307,13 @@
         <v>150</v>
       </c>
       <c r="B6" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="C6" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="D6" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="E6"/>
       <c r="F6"/>
@@ -10222,13 +10325,13 @@
         <v>172</v>
       </c>
       <c r="B7" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="C7" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="D7" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="E7"/>
       <c r="F7"/>
@@ -10240,13 +10343,13 @@
         <v>175</v>
       </c>
       <c r="B8" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="C8" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="D8" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="E8"/>
       <c r="F8"/>
@@ -10258,13 +10361,13 @@
         <v>183</v>
       </c>
       <c r="B9" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="C9" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="D9" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="E9"/>
       <c r="F9"/>
@@ -10276,13 +10379,13 @@
         <v>188</v>
       </c>
       <c r="B10" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="C10" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="D10" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="E10"/>
       <c r="F10"/>
@@ -10294,13 +10397,13 @@
         <v>191</v>
       </c>
       <c r="B11" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="C11" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="D11" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="E11"/>
       <c r="F11"/>
@@ -10312,13 +10415,13 @@
         <v>197</v>
       </c>
       <c r="B12" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="C12" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="D12" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="E12"/>
       <c r="F12"/>
@@ -10330,13 +10433,13 @@
         <v>200</v>
       </c>
       <c r="B13" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="C13" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="D13" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="E13"/>
       <c r="F13"/>
@@ -10348,13 +10451,13 @@
         <v>203</v>
       </c>
       <c r="B14" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="C14" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="D14" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="E14"/>
       <c r="F14"/>
@@ -10366,13 +10469,13 @@
         <v>206</v>
       </c>
       <c r="B15" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="C15" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="D15" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="E15"/>
       <c r="F15"/>
@@ -10384,13 +10487,13 @@
         <v>209</v>
       </c>
       <c r="B16" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="C16" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="D16" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="E16"/>
       <c r="F16"/>
@@ -10402,13 +10505,13 @@
         <v>214</v>
       </c>
       <c r="B17" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="C17" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="D17" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="E17"/>
       <c r="F17"/>
@@ -10420,13 +10523,13 @@
         <v>219</v>
       </c>
       <c r="B18" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="C18" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="D18" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="E18"/>
       <c r="F18"/>
@@ -10438,13 +10541,13 @@
         <v>225</v>
       </c>
       <c r="B19" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="C19" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="D19" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="E19"/>
       <c r="F19"/>
@@ -10456,13 +10559,13 @@
         <v>235</v>
       </c>
       <c r="B20" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="C20" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="D20" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="E20"/>
       <c r="F20"/>
@@ -10474,13 +10577,13 @@
         <v>240</v>
       </c>
       <c r="B21" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="C21" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="D21" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="E21"/>
       <c r="F21"/>
@@ -10492,13 +10595,13 @@
         <v>249</v>
       </c>
       <c r="B22" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="C22" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="D22" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="E22"/>
       <c r="F22"/>
@@ -10510,13 +10613,13 @@
         <v>252</v>
       </c>
       <c r="B23" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="C23" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="D23" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="E23"/>
       <c r="F23"/>
@@ -10528,13 +10631,13 @@
         <v>255</v>
       </c>
       <c r="B24" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="C24" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="D24" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="E24"/>
       <c r="F24"/>
@@ -10546,13 +10649,13 @@
         <v>258</v>
       </c>
       <c r="B25" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="C25" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="D25" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="E25"/>
       <c r="F25"/>
@@ -10564,13 +10667,13 @@
         <v>266</v>
       </c>
       <c r="B26" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="C26" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="D26" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="E26"/>
       <c r="F26"/>
@@ -10582,13 +10685,13 @@
         <v>269</v>
       </c>
       <c r="B27" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="C27" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="D27" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="E27"/>
       <c r="F27"/>
@@ -10600,13 +10703,13 @@
         <v>272</v>
       </c>
       <c r="B28" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="C28" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="D28" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="E28"/>
       <c r="F28"/>
@@ -10618,13 +10721,13 @@
         <v>275</v>
       </c>
       <c r="B29" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="C29" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="D29" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="E29"/>
       <c r="F29"/>
@@ -10636,13 +10739,13 @@
         <v>278</v>
       </c>
       <c r="B30" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="C30" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="D30" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="E30"/>
       <c r="F30"/>
@@ -10654,13 +10757,13 @@
         <v>284</v>
       </c>
       <c r="B31" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="C31" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="D31" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="E31"/>
       <c r="F31"/>
@@ -10672,13 +10775,13 @@
         <v>287</v>
       </c>
       <c r="B32" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="C32" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="D32" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="E32"/>
       <c r="F32"/>
@@ -10690,13 +10793,13 @@
         <v>292</v>
       </c>
       <c r="B33" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="C33" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="D33" t="s">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="E33"/>
       <c r="F33"/>
@@ -10708,13 +10811,13 @@
         <v>301</v>
       </c>
       <c r="B34" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="C34" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="D34" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="E34"/>
       <c r="F34"/>
@@ -10726,13 +10829,13 @@
         <v>309</v>
       </c>
       <c r="B35" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="C35" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="D35" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="E35"/>
       <c r="F35"/>
@@ -10744,13 +10847,13 @@
         <v>327</v>
       </c>
       <c r="B36" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="C36" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="D36" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="E36"/>
       <c r="F36"/>
@@ -10762,13 +10865,13 @@
         <v>328</v>
       </c>
       <c r="B37" t="s">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="C37" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="D37" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="E37"/>
       <c r="F37"/>
@@ -10780,13 +10883,13 @@
         <v>331</v>
       </c>
       <c r="B38" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="C38" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="D38" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="E38"/>
       <c r="F38"/>
@@ -10798,13 +10901,13 @@
         <v>333</v>
       </c>
       <c r="B39" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="C39" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="D39" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="E39"/>
       <c r="F39"/>
@@ -10816,13 +10919,13 @@
         <v>342</v>
       </c>
       <c r="B40" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="C40" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="D40" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="E40"/>
       <c r="F40"/>
@@ -10834,13 +10937,13 @@
         <v>343</v>
       </c>
       <c r="B41" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="C41" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="D41" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="E41"/>
       <c r="F41"/>
@@ -10852,13 +10955,13 @@
         <v>346</v>
       </c>
       <c r="B42" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="C42" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="D42" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="E42"/>
       <c r="F42"/>
@@ -10867,16 +10970,16 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B43" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="C43" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="D43" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="E43"/>
       <c r="F43"/>
@@ -10885,16 +10988,16 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B44" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="C44" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="D44" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="E44"/>
       <c r="F44"/>
@@ -10903,16 +11006,16 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B45" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="C45" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="D45" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="E45"/>
       <c r="F45"/>
@@ -10921,16 +11024,16 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>374</v>
+        <v>353</v>
       </c>
       <c r="B46" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="C46" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="D46" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="E46"/>
       <c r="F46"/>
@@ -10939,16 +11042,16 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>398</v>
+        <v>377</v>
       </c>
       <c r="B47" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="C47" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="D47" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="E47"/>
       <c r="F47"/>
@@ -10957,16 +11060,16 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="B48" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="C48" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="D48" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="E48"/>
       <c r="F48"/>
@@ -10975,21 +11078,39 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="B49" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="C49" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="D49" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="E49"/>
       <c r="F49"/>
       <c r="G49"/>
       <c r="H49"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>415</v>
+      </c>
+      <c r="B50" t="s">
+        <v>593</v>
+      </c>
+      <c r="C50" t="s">
+        <v>497</v>
+      </c>
+      <c r="D50" t="s">
+        <v>594</v>
+      </c>
+      <c r="E50"/>
+      <c r="F50"/>
+      <c r="G50"/>
+      <c r="H50"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11004,13 +11125,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="B1" t="s">
         <v>10</v>
       </c>
       <c r="C1" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="D1" t="s">
         <v>49</v>
@@ -11018,7 +11139,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>588</v>
+        <v>595</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>

--- a/study/03_adam/spec/adam_spec.xlsx
+++ b/study/03_adam/spec/adam_spec.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">Note</t>
   </si>
   <si>
-    <t xml:space="preserve">Synthetic data only: simulated for a portfolio worked example; not real trial data and not a regulatory deliverable.</t>
+    <t xml:space="preserve">Synthetic data only: simulated for this worked example; not real trial data and not a regulatory deliverable.</t>
   </si>
   <si>
     <t xml:space="preserve">Dataset</t>
